--- a/data/misc./skip_conditions_final.xlsx
+++ b/data/misc./skip_conditions_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Desktop/CES Accuracy Analysis/data/misc./"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Repos/CES Accuracy Analysis/data/misc./"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA32BE84-1F24-1B44-B6FE-270E20EBF678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C60A78-FD80-E248-ABDE-A4BCEB5BF8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1180" windowWidth="34560" windowHeight="20420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="87">
   <si>
     <t>State</t>
   </si>
@@ -344,7 +344,49 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -672,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E860"/>
+  <dimension ref="A1:E862"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="25" customWidth="1"/>
@@ -4679,7 +4721,7 @@
         <v>35</v>
       </c>
       <c r="B236">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C236" t="s">
         <v>8</v>
@@ -4688,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
@@ -4696,7 +4738,7 @@
         <v>35</v>
       </c>
       <c r="B237">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C237" t="s">
         <v>27</v>
@@ -4705,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
@@ -4713,16 +4755,16 @@
         <v>35</v>
       </c>
       <c r="B238">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C238" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D238" t="b">
         <v>1</v>
       </c>
       <c r="E238" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
@@ -4730,27 +4772,27 @@
         <v>35</v>
       </c>
       <c r="B239">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C239" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D239" t="b">
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B240">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C240" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D240" t="b">
         <v>1</v>
@@ -4761,13 +4803,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B241">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C241" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D241" t="b">
         <v>1</v>
@@ -4784,7 +4826,7 @@
         <v>2010</v>
       </c>
       <c r="C242" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D242" t="b">
         <v>1</v>
@@ -4801,7 +4843,7 @@
         <v>2010</v>
       </c>
       <c r="C243" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D243" t="b">
         <v>1</v>
@@ -4815,10 +4857,10 @@
         <v>36</v>
       </c>
       <c r="B244">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C244" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D244" t="b">
         <v>1</v>
@@ -4832,10 +4874,10 @@
         <v>36</v>
       </c>
       <c r="B245">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C245" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D245" t="b">
         <v>1</v>
@@ -4852,7 +4894,7 @@
         <v>2012</v>
       </c>
       <c r="C246" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D246" t="b">
         <v>1</v>
@@ -4869,7 +4911,7 @@
         <v>2012</v>
       </c>
       <c r="C247" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D247" t="b">
         <v>1</v>
@@ -4883,10 +4925,10 @@
         <v>36</v>
       </c>
       <c r="B248">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C248" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D248" t="b">
         <v>1</v>
@@ -4900,10 +4942,10 @@
         <v>36</v>
       </c>
       <c r="B249">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C249" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D249" t="b">
         <v>1</v>
@@ -4920,7 +4962,7 @@
         <v>2014</v>
       </c>
       <c r="C250" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D250" t="b">
         <v>1</v>
@@ -4937,7 +4979,7 @@
         <v>2014</v>
       </c>
       <c r="C251" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D251" t="b">
         <v>1</v>
@@ -4951,10 +4993,10 @@
         <v>36</v>
       </c>
       <c r="B252">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C252" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D252" t="b">
         <v>1</v>
@@ -4968,10 +5010,10 @@
         <v>36</v>
       </c>
       <c r="B253">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C253" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D253" t="b">
         <v>1</v>
@@ -4988,7 +5030,7 @@
         <v>2016</v>
       </c>
       <c r="C254" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D254" t="b">
         <v>1</v>
@@ -5005,7 +5047,7 @@
         <v>2016</v>
       </c>
       <c r="C255" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D255" t="b">
         <v>1</v>
@@ -5019,10 +5061,10 @@
         <v>36</v>
       </c>
       <c r="B256">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C256" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D256" t="b">
         <v>1</v>
@@ -5036,10 +5078,10 @@
         <v>36</v>
       </c>
       <c r="B257">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C257" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D257" t="b">
         <v>1</v>
@@ -5056,7 +5098,7 @@
         <v>2018</v>
       </c>
       <c r="C258" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D258" t="b">
         <v>1</v>
@@ -5073,7 +5115,7 @@
         <v>2018</v>
       </c>
       <c r="C259" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D259" t="b">
         <v>1</v>
@@ -5084,13 +5126,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B260">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C260" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D260" t="b">
         <v>1</v>
@@ -5101,13 +5143,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B261">
-        <v>2008</v>
+        <v>2018</v>
       </c>
       <c r="C261" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D261" t="b">
         <v>1</v>
@@ -5124,7 +5166,7 @@
         <v>2008</v>
       </c>
       <c r="C262" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D262" t="b">
         <v>1</v>
@@ -5141,7 +5183,7 @@
         <v>2008</v>
       </c>
       <c r="C263" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D263" t="b">
         <v>1</v>
@@ -5155,10 +5197,10 @@
         <v>37</v>
       </c>
       <c r="B264">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C264" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D264" t="b">
         <v>1</v>
@@ -5172,10 +5214,10 @@
         <v>37</v>
       </c>
       <c r="B265">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C265" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D265" t="b">
         <v>1</v>
@@ -5192,7 +5234,7 @@
         <v>2010</v>
       </c>
       <c r="C266" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D266" t="b">
         <v>1</v>
@@ -5209,7 +5251,7 @@
         <v>2010</v>
       </c>
       <c r="C267" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D267" t="b">
         <v>1</v>
@@ -5226,7 +5268,7 @@
         <v>2010</v>
       </c>
       <c r="C268" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D268" t="b">
         <v>1</v>
@@ -5243,7 +5285,7 @@
         <v>2010</v>
       </c>
       <c r="C269" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D269" t="b">
         <v>1</v>
@@ -5260,7 +5302,7 @@
         <v>2010</v>
       </c>
       <c r="C270" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D270" t="b">
         <v>1</v>
@@ -5277,7 +5319,7 @@
         <v>2010</v>
       </c>
       <c r="C271" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D271" t="b">
         <v>1</v>
@@ -5291,10 +5333,10 @@
         <v>37</v>
       </c>
       <c r="B272">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C272" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D272" t="b">
         <v>1</v>
@@ -5308,10 +5350,10 @@
         <v>37</v>
       </c>
       <c r="B273">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C273" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D273" t="b">
         <v>1</v>
@@ -5328,7 +5370,7 @@
         <v>2012</v>
       </c>
       <c r="C274" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D274" t="b">
         <v>1</v>
@@ -5345,7 +5387,7 @@
         <v>2012</v>
       </c>
       <c r="C275" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D275" t="b">
         <v>1</v>
@@ -5362,7 +5404,7 @@
         <v>2012</v>
       </c>
       <c r="C276" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D276" t="b">
         <v>1</v>
@@ -5379,7 +5421,7 @@
         <v>2012</v>
       </c>
       <c r="C277" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D277" t="b">
         <v>1</v>
@@ -5396,7 +5438,7 @@
         <v>2012</v>
       </c>
       <c r="C278" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D278" t="b">
         <v>1</v>
@@ -5413,7 +5455,7 @@
         <v>2012</v>
       </c>
       <c r="C279" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D279" t="b">
         <v>1</v>
@@ -5427,10 +5469,10 @@
         <v>37</v>
       </c>
       <c r="B280">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C280" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D280" t="b">
         <v>1</v>
@@ -5444,10 +5486,10 @@
         <v>37</v>
       </c>
       <c r="B281">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C281" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D281" t="b">
         <v>1</v>
@@ -5464,7 +5506,7 @@
         <v>2014</v>
       </c>
       <c r="C282" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D282" t="b">
         <v>1</v>
@@ -5481,7 +5523,7 @@
         <v>2014</v>
       </c>
       <c r="C283" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D283" t="b">
         <v>1</v>
@@ -5498,7 +5540,7 @@
         <v>2014</v>
       </c>
       <c r="C284" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D284" t="b">
         <v>1</v>
@@ -5515,7 +5557,7 @@
         <v>2014</v>
       </c>
       <c r="C285" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D285" t="b">
         <v>1</v>
@@ -5532,7 +5574,7 @@
         <v>2014</v>
       </c>
       <c r="C286" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D286" t="b">
         <v>1</v>
@@ -5549,7 +5591,7 @@
         <v>2014</v>
       </c>
       <c r="C287" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D287" t="b">
         <v>1</v>
@@ -5563,10 +5605,10 @@
         <v>37</v>
       </c>
       <c r="B288">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C288" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D288" t="b">
         <v>1</v>
@@ -5580,10 +5622,10 @@
         <v>37</v>
       </c>
       <c r="B289">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C289" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D289" t="b">
         <v>1</v>
@@ -5600,7 +5642,7 @@
         <v>2016</v>
       </c>
       <c r="C290" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D290" t="b">
         <v>1</v>
@@ -5617,7 +5659,7 @@
         <v>2016</v>
       </c>
       <c r="C291" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D291" t="b">
         <v>1</v>
@@ -5634,7 +5676,7 @@
         <v>2016</v>
       </c>
       <c r="C292" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D292" t="b">
         <v>1</v>
@@ -5651,7 +5693,7 @@
         <v>2016</v>
       </c>
       <c r="C293" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D293" t="b">
         <v>1</v>
@@ -5668,7 +5710,7 @@
         <v>2016</v>
       </c>
       <c r="C294" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D294" t="b">
         <v>1</v>
@@ -5685,7 +5727,7 @@
         <v>2016</v>
       </c>
       <c r="C295" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D295" t="b">
         <v>1</v>
@@ -5699,7 +5741,7 @@
         <v>37</v>
       </c>
       <c r="B296">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C296" t="s">
         <v>8</v>
@@ -5716,7 +5758,7 @@
         <v>37</v>
       </c>
       <c r="B297">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C297" t="s">
         <v>27</v>
@@ -5736,13 +5778,13 @@
         <v>2018</v>
       </c>
       <c r="C298" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D298" t="b">
         <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
@@ -5753,13 +5795,13 @@
         <v>2018</v>
       </c>
       <c r="C299" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D299" t="b">
         <v>1</v>
       </c>
       <c r="E299" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
@@ -5767,16 +5809,16 @@
         <v>37</v>
       </c>
       <c r="B300">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C300" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D300" t="b">
         <v>1</v>
       </c>
       <c r="E300" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
@@ -5784,16 +5826,16 @@
         <v>37</v>
       </c>
       <c r="B301">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C301" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D301" t="b">
         <v>1</v>
       </c>
       <c r="E301" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
@@ -5804,7 +5846,7 @@
         <v>2020</v>
       </c>
       <c r="C302" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D302" t="b">
         <v>1</v>
@@ -5821,7 +5863,7 @@
         <v>2020</v>
       </c>
       <c r="C303" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D303" t="b">
         <v>1</v>
@@ -5835,10 +5877,10 @@
         <v>37</v>
       </c>
       <c r="B304">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C304" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D304" t="b">
         <v>1</v>
@@ -5852,10 +5894,10 @@
         <v>37</v>
       </c>
       <c r="B305">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C305" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D305" t="b">
         <v>1</v>
@@ -5872,7 +5914,7 @@
         <v>2022</v>
       </c>
       <c r="C306" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D306" t="b">
         <v>1</v>
@@ -5889,7 +5931,7 @@
         <v>2022</v>
       </c>
       <c r="C307" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D307" t="b">
         <v>1</v>
@@ -5900,36 +5942,36 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B308">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C308" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D308" t="b">
         <v>1</v>
       </c>
       <c r="E308" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B309">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C309" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D309" t="b">
         <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
@@ -5940,7 +5982,7 @@
         <v>2006</v>
       </c>
       <c r="C310" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D310" t="b">
         <v>1</v>
@@ -5957,7 +5999,7 @@
         <v>2006</v>
       </c>
       <c r="C311" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D311" t="b">
         <v>1</v>
@@ -5971,10 +6013,10 @@
         <v>38</v>
       </c>
       <c r="B312">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C312" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D312" t="b">
         <v>1</v>
@@ -5988,10 +6030,10 @@
         <v>38</v>
       </c>
       <c r="B313">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C313" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D313" t="b">
         <v>1</v>
@@ -6008,7 +6050,7 @@
         <v>2010</v>
       </c>
       <c r="C314" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D314" t="b">
         <v>1</v>
@@ -6025,7 +6067,7 @@
         <v>2010</v>
       </c>
       <c r="C315" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D315" t="b">
         <v>1</v>
@@ -6039,10 +6081,10 @@
         <v>38</v>
       </c>
       <c r="B316">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C316" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D316" t="b">
         <v>1</v>
@@ -6056,10 +6098,10 @@
         <v>38</v>
       </c>
       <c r="B317">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C317" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D317" t="b">
         <v>1</v>
@@ -6076,7 +6118,7 @@
         <v>2012</v>
       </c>
       <c r="C318" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D318" t="b">
         <v>1</v>
@@ -6093,7 +6135,7 @@
         <v>2012</v>
       </c>
       <c r="C319" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D319" t="b">
         <v>1</v>
@@ -6107,10 +6149,10 @@
         <v>38</v>
       </c>
       <c r="B320">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C320" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D320" t="b">
         <v>1</v>
@@ -6124,10 +6166,10 @@
         <v>38</v>
       </c>
       <c r="B321">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C321" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D321" t="b">
         <v>1</v>
@@ -6144,7 +6186,7 @@
         <v>2014</v>
       </c>
       <c r="C322" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D322" t="b">
         <v>1</v>
@@ -6161,7 +6203,7 @@
         <v>2014</v>
       </c>
       <c r="C323" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D323" t="b">
         <v>1</v>
@@ -6175,10 +6217,10 @@
         <v>38</v>
       </c>
       <c r="B324">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C324" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D324" t="b">
         <v>1</v>
@@ -6192,10 +6234,10 @@
         <v>38</v>
       </c>
       <c r="B325">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C325" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D325" t="b">
         <v>1</v>
@@ -6212,7 +6254,7 @@
         <v>2016</v>
       </c>
       <c r="C326" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D326" t="b">
         <v>1</v>
@@ -6229,7 +6271,7 @@
         <v>2016</v>
       </c>
       <c r="C327" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D327" t="b">
         <v>1</v>
@@ -6240,10 +6282,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B328">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C328" t="s">
         <v>10</v>
@@ -6257,10 +6299,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B329">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C329" t="s">
         <v>13</v>
@@ -6277,16 +6319,16 @@
         <v>39</v>
       </c>
       <c r="B330">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C330" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D330" t="b">
         <v>1</v>
       </c>
       <c r="E330" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
@@ -6294,16 +6336,16 @@
         <v>39</v>
       </c>
       <c r="B331">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C331" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D331" t="b">
         <v>1</v>
       </c>
       <c r="E331" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
@@ -6314,7 +6356,7 @@
         <v>2008</v>
       </c>
       <c r="C332" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D332" t="b">
         <v>1</v>
@@ -6331,7 +6373,7 @@
         <v>2008</v>
       </c>
       <c r="C333" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D333" t="b">
         <v>1</v>
@@ -6345,16 +6387,16 @@
         <v>39</v>
       </c>
       <c r="B334">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C334" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D334" t="b">
         <v>1</v>
       </c>
       <c r="E334" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
@@ -6362,16 +6404,16 @@
         <v>39</v>
       </c>
       <c r="B335">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C335" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D335" t="b">
         <v>1</v>
       </c>
       <c r="E335" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
@@ -6379,16 +6421,16 @@
         <v>39</v>
       </c>
       <c r="B336">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C336" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D336" t="b">
         <v>1</v>
       </c>
       <c r="E336" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
@@ -6396,16 +6438,16 @@
         <v>39</v>
       </c>
       <c r="B337">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C337" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D337" t="b">
         <v>1</v>
       </c>
       <c r="E337" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
@@ -6416,13 +6458,13 @@
         <v>2012</v>
       </c>
       <c r="C338" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D338" t="b">
         <v>1</v>
       </c>
       <c r="E338" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
@@ -6433,13 +6475,13 @@
         <v>2012</v>
       </c>
       <c r="C339" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D339" t="b">
         <v>1</v>
       </c>
       <c r="E339" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
@@ -6450,13 +6492,13 @@
         <v>2012</v>
       </c>
       <c r="C340" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D340" t="b">
         <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
@@ -6467,13 +6509,13 @@
         <v>2012</v>
       </c>
       <c r="C341" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D341" t="b">
         <v>1</v>
       </c>
       <c r="E341" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
@@ -6484,7 +6526,7 @@
         <v>2012</v>
       </c>
       <c r="C342" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D342" t="b">
         <v>1</v>
@@ -6501,7 +6543,7 @@
         <v>2012</v>
       </c>
       <c r="C343" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D343" t="b">
         <v>1</v>
@@ -6515,16 +6557,16 @@
         <v>39</v>
       </c>
       <c r="B344">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C344" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D344" t="b">
         <v>1</v>
       </c>
       <c r="E344" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
@@ -6532,16 +6574,16 @@
         <v>39</v>
       </c>
       <c r="B345">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C345" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D345" t="b">
         <v>1</v>
       </c>
       <c r="E345" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
@@ -6549,16 +6591,16 @@
         <v>39</v>
       </c>
       <c r="B346">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C346" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D346" t="b">
         <v>1</v>
       </c>
       <c r="E346" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
@@ -6566,16 +6608,16 @@
         <v>39</v>
       </c>
       <c r="B347">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C347" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D347" t="b">
         <v>1</v>
       </c>
       <c r="E347" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
@@ -6586,13 +6628,13 @@
         <v>2016</v>
       </c>
       <c r="C348" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D348" t="b">
         <v>1</v>
       </c>
       <c r="E348" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
@@ -6603,13 +6645,13 @@
         <v>2016</v>
       </c>
       <c r="C349" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D349" t="b">
         <v>1</v>
       </c>
       <c r="E349" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
@@ -6620,13 +6662,13 @@
         <v>2016</v>
       </c>
       <c r="C350" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D350" t="b">
         <v>1</v>
       </c>
       <c r="E350" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
@@ -6637,13 +6679,13 @@
         <v>2016</v>
       </c>
       <c r="C351" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D351" t="b">
         <v>1</v>
       </c>
       <c r="E351" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
@@ -6654,7 +6696,7 @@
         <v>2016</v>
       </c>
       <c r="C352" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D352" t="b">
         <v>1</v>
@@ -6671,7 +6713,7 @@
         <v>2016</v>
       </c>
       <c r="C353" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D353" t="b">
         <v>1</v>
@@ -6685,10 +6727,10 @@
         <v>39</v>
       </c>
       <c r="B354">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C354" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D354" t="b">
         <v>1</v>
@@ -6702,10 +6744,10 @@
         <v>39</v>
       </c>
       <c r="B355">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C355" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D355" t="b">
         <v>1</v>
@@ -6722,7 +6764,7 @@
         <v>2020</v>
       </c>
       <c r="C356" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D356" t="b">
         <v>1</v>
@@ -6739,7 +6781,7 @@
         <v>2020</v>
       </c>
       <c r="C357" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D357" t="b">
         <v>1</v>
@@ -6750,13 +6792,13 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B358">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C358" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D358" t="b">
         <v>1</v>
@@ -6767,13 +6809,13 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B359">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C359" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D359" t="b">
         <v>1</v>
@@ -6790,7 +6832,7 @@
         <v>2012</v>
       </c>
       <c r="C360" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D360" t="b">
         <v>1</v>
@@ -6807,7 +6849,7 @@
         <v>2012</v>
       </c>
       <c r="C361" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D361" t="b">
         <v>1</v>
@@ -6821,10 +6863,10 @@
         <v>40</v>
       </c>
       <c r="B362">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C362" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D362" t="b">
         <v>1</v>
@@ -6838,10 +6880,10 @@
         <v>40</v>
       </c>
       <c r="B363">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C363" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D363" t="b">
         <v>1</v>
@@ -6858,7 +6900,7 @@
         <v>2016</v>
       </c>
       <c r="C364" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D364" t="b">
         <v>1</v>
@@ -6875,7 +6917,7 @@
         <v>2016</v>
       </c>
       <c r="C365" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D365" t="b">
         <v>1</v>
@@ -6886,13 +6928,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B366">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C366" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D366" t="b">
         <v>1</v>
@@ -6903,13 +6945,13 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B367">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C367" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D367" t="b">
         <v>1</v>
@@ -6923,10 +6965,10 @@
         <v>41</v>
       </c>
       <c r="B368">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C368" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D368" t="b">
         <v>1</v>
@@ -6940,10 +6982,10 @@
         <v>41</v>
       </c>
       <c r="B369">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C369" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D369" t="b">
         <v>1</v>
@@ -6960,7 +7002,7 @@
         <v>2012</v>
       </c>
       <c r="C370" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D370" t="b">
         <v>1</v>
@@ -6977,7 +7019,7 @@
         <v>2012</v>
       </c>
       <c r="C371" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D371" t="b">
         <v>1</v>
@@ -6994,7 +7036,7 @@
         <v>2012</v>
       </c>
       <c r="C372" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D372" t="b">
         <v>1</v>
@@ -7011,7 +7053,7 @@
         <v>2012</v>
       </c>
       <c r="C373" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D373" t="b">
         <v>1</v>
@@ -7025,10 +7067,10 @@
         <v>41</v>
       </c>
       <c r="B374">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C374" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D374" t="b">
         <v>1</v>
@@ -7042,10 +7084,10 @@
         <v>41</v>
       </c>
       <c r="B375">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C375" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D375" t="b">
         <v>1</v>
@@ -7062,7 +7104,7 @@
         <v>2016</v>
       </c>
       <c r="C376" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D376" t="b">
         <v>1</v>
@@ -7079,7 +7121,7 @@
         <v>2016</v>
       </c>
       <c r="C377" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D377" t="b">
         <v>1</v>
@@ -7096,7 +7138,7 @@
         <v>2016</v>
       </c>
       <c r="C378" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D378" t="b">
         <v>1</v>
@@ -7113,7 +7155,7 @@
         <v>2016</v>
       </c>
       <c r="C379" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D379" t="b">
         <v>1</v>
@@ -7127,7 +7169,7 @@
         <v>41</v>
       </c>
       <c r="B380">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C380" t="s">
         <v>8</v>
@@ -7144,7 +7186,7 @@
         <v>41</v>
       </c>
       <c r="B381">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C381" t="s">
         <v>27</v>
@@ -7158,13 +7200,13 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B382">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C382" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D382" t="b">
         <v>1</v>
@@ -7175,13 +7217,13 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B383">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C383" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D383" t="b">
         <v>1</v>
@@ -7195,10 +7237,10 @@
         <v>42</v>
       </c>
       <c r="B384">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C384" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D384" t="b">
         <v>1</v>
@@ -7212,10 +7254,10 @@
         <v>42</v>
       </c>
       <c r="B385">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="C385" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D385" t="b">
         <v>1</v>
@@ -7232,7 +7274,7 @@
         <v>2012</v>
       </c>
       <c r="C386" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D386" t="b">
         <v>1</v>
@@ -7249,7 +7291,7 @@
         <v>2012</v>
       </c>
       <c r="C387" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D387" t="b">
         <v>1</v>
@@ -7263,10 +7305,10 @@
         <v>42</v>
       </c>
       <c r="B388">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C388" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D388" t="b">
         <v>1</v>
@@ -7280,10 +7322,10 @@
         <v>42</v>
       </c>
       <c r="B389">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C389" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D389" t="b">
         <v>1</v>
@@ -7297,10 +7339,10 @@
         <v>42</v>
       </c>
       <c r="B390">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C390" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D390" t="b">
         <v>1</v>
@@ -7314,10 +7356,10 @@
         <v>42</v>
       </c>
       <c r="B391">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C391" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D391" t="b">
         <v>1</v>
@@ -7334,7 +7376,7 @@
         <v>2016</v>
       </c>
       <c r="C392" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D392" t="b">
         <v>1</v>
@@ -7351,7 +7393,7 @@
         <v>2016</v>
       </c>
       <c r="C393" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D393" t="b">
         <v>1</v>
@@ -7362,13 +7404,13 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B394">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C394" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D394" t="b">
         <v>1</v>
@@ -7379,13 +7421,13 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B395">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C395" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D395" t="b">
         <v>1</v>
@@ -7402,7 +7444,7 @@
         <v>2008</v>
       </c>
       <c r="C396" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D396" t="b">
         <v>1</v>
@@ -7419,7 +7461,7 @@
         <v>2008</v>
       </c>
       <c r="C397" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D397" t="b">
         <v>1</v>
@@ -7433,10 +7475,10 @@
         <v>43</v>
       </c>
       <c r="B398">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C398" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D398" t="b">
         <v>1</v>
@@ -7450,10 +7492,10 @@
         <v>43</v>
       </c>
       <c r="B399">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C399" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D399" t="b">
         <v>1</v>
@@ -7470,7 +7512,7 @@
         <v>2010</v>
       </c>
       <c r="C400" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D400" t="b">
         <v>1</v>
@@ -7487,7 +7529,7 @@
         <v>2010</v>
       </c>
       <c r="C401" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D401" t="b">
         <v>1</v>
@@ -7504,7 +7546,7 @@
         <v>2010</v>
       </c>
       <c r="C402" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D402" t="b">
         <v>1</v>
@@ -7521,7 +7563,7 @@
         <v>2010</v>
       </c>
       <c r="C403" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D403" t="b">
         <v>1</v>
@@ -7538,7 +7580,7 @@
         <v>2010</v>
       </c>
       <c r="C404" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D404" t="b">
         <v>1</v>
@@ -7555,7 +7597,7 @@
         <v>2010</v>
       </c>
       <c r="C405" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D405" t="b">
         <v>1</v>
@@ -7569,10 +7611,10 @@
         <v>43</v>
       </c>
       <c r="B406">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C406" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D406" t="b">
         <v>1</v>
@@ -7586,10 +7628,10 @@
         <v>43</v>
       </c>
       <c r="B407">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C407" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D407" t="b">
         <v>1</v>
@@ -7606,7 +7648,7 @@
         <v>2012</v>
       </c>
       <c r="C408" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D408" t="b">
         <v>1</v>
@@ -7623,7 +7665,7 @@
         <v>2012</v>
       </c>
       <c r="C409" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D409" t="b">
         <v>1</v>
@@ -7640,7 +7682,7 @@
         <v>2012</v>
       </c>
       <c r="C410" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D410" t="b">
         <v>1</v>
@@ -7657,7 +7699,7 @@
         <v>2012</v>
       </c>
       <c r="C411" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D411" t="b">
         <v>1</v>
@@ -7674,7 +7716,7 @@
         <v>2012</v>
       </c>
       <c r="C412" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D412" t="b">
         <v>1</v>
@@ -7691,7 +7733,7 @@
         <v>2012</v>
       </c>
       <c r="C413" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D413" t="b">
         <v>1</v>
@@ -7705,10 +7747,10 @@
         <v>43</v>
       </c>
       <c r="B414">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C414" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D414" t="b">
         <v>1</v>
@@ -7722,10 +7764,10 @@
         <v>43</v>
       </c>
       <c r="B415">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C415" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D415" t="b">
         <v>1</v>
@@ -7742,7 +7784,7 @@
         <v>2014</v>
       </c>
       <c r="C416" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D416" t="b">
         <v>1</v>
@@ -7759,7 +7801,7 @@
         <v>2014</v>
       </c>
       <c r="C417" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D417" t="b">
         <v>1</v>
@@ -7776,7 +7818,7 @@
         <v>2014</v>
       </c>
       <c r="C418" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D418" t="b">
         <v>1</v>
@@ -7793,7 +7835,7 @@
         <v>2014</v>
       </c>
       <c r="C419" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D419" t="b">
         <v>1</v>
@@ -7810,7 +7852,7 @@
         <v>2014</v>
       </c>
       <c r="C420" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D420" t="b">
         <v>1</v>
@@ -7827,7 +7869,7 @@
         <v>2014</v>
       </c>
       <c r="C421" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D421" t="b">
         <v>1</v>
@@ -7841,10 +7883,10 @@
         <v>43</v>
       </c>
       <c r="B422">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C422" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D422" t="b">
         <v>1</v>
@@ -7858,10 +7900,10 @@
         <v>43</v>
       </c>
       <c r="B423">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C423" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D423" t="b">
         <v>1</v>
@@ -7878,7 +7920,7 @@
         <v>2016</v>
       </c>
       <c r="C424" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D424" t="b">
         <v>1</v>
@@ -7895,7 +7937,7 @@
         <v>2016</v>
       </c>
       <c r="C425" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D425" t="b">
         <v>1</v>
@@ -7912,7 +7954,7 @@
         <v>2016</v>
       </c>
       <c r="C426" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D426" t="b">
         <v>1</v>
@@ -7929,7 +7971,7 @@
         <v>2016</v>
       </c>
       <c r="C427" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D427" t="b">
         <v>1</v>
@@ -7946,7 +7988,7 @@
         <v>2016</v>
       </c>
       <c r="C428" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D428" t="b">
         <v>1</v>
@@ -7963,7 +8005,7 @@
         <v>2016</v>
       </c>
       <c r="C429" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D429" t="b">
         <v>1</v>
@@ -7977,7 +8019,7 @@
         <v>43</v>
       </c>
       <c r="B430">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C430" t="s">
         <v>8</v>
@@ -7994,7 +8036,7 @@
         <v>43</v>
       </c>
       <c r="B431">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C431" t="s">
         <v>27</v>
@@ -8014,13 +8056,13 @@
         <v>2018</v>
       </c>
       <c r="C432" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D432" t="b">
         <v>1</v>
       </c>
       <c r="E432" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.2">
@@ -8031,13 +8073,13 @@
         <v>2018</v>
       </c>
       <c r="C433" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D433" t="b">
         <v>1</v>
       </c>
       <c r="E433" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.2">
@@ -8045,16 +8087,16 @@
         <v>43</v>
       </c>
       <c r="B434">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C434" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D434" t="b">
         <v>1</v>
       </c>
       <c r="E434" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.2">
@@ -8062,16 +8104,16 @@
         <v>43</v>
       </c>
       <c r="B435">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C435" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D435" t="b">
         <v>1</v>
       </c>
       <c r="E435" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.2">
@@ -8082,7 +8124,7 @@
         <v>2020</v>
       </c>
       <c r="C436" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D436" t="b">
         <v>1</v>
@@ -8099,7 +8141,7 @@
         <v>2020</v>
       </c>
       <c r="C437" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D437" t="b">
         <v>1</v>
@@ -8113,16 +8155,16 @@
         <v>43</v>
       </c>
       <c r="B438">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C438" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D438" t="b">
         <v>1</v>
       </c>
       <c r="E438" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.2">
@@ -8130,16 +8172,16 @@
         <v>43</v>
       </c>
       <c r="B439">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C439" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D439" t="b">
         <v>1</v>
       </c>
       <c r="E439" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.2">
@@ -8150,13 +8192,13 @@
         <v>2022</v>
       </c>
       <c r="C440" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D440" t="b">
         <v>1</v>
       </c>
       <c r="E440" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.2">
@@ -8167,47 +8209,47 @@
         <v>2022</v>
       </c>
       <c r="C441" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D441" t="b">
         <v>1</v>
       </c>
       <c r="E441" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B442">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C442" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D442" t="b">
         <v>1</v>
       </c>
       <c r="E442" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B443">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C443" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D443" t="b">
         <v>1</v>
       </c>
       <c r="E443" t="s">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.2">
@@ -8218,7 +8260,7 @@
         <v>2010</v>
       </c>
       <c r="C444" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D444" t="b">
         <v>1</v>
@@ -8235,7 +8277,7 @@
         <v>2010</v>
       </c>
       <c r="C445" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D445" t="b">
         <v>1</v>
@@ -8249,10 +8291,10 @@
         <v>44</v>
       </c>
       <c r="B446">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C446" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D446" t="b">
         <v>1</v>
@@ -8266,10 +8308,10 @@
         <v>44</v>
       </c>
       <c r="B447">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C447" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D447" t="b">
         <v>1</v>
@@ -8286,7 +8328,7 @@
         <v>2014</v>
       </c>
       <c r="C448" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D448" t="b">
         <v>1</v>
@@ -8303,7 +8345,7 @@
         <v>2014</v>
       </c>
       <c r="C449" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D449" t="b">
         <v>1</v>
@@ -8314,13 +8356,13 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B450">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C450" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D450" t="b">
         <v>1</v>
@@ -8331,13 +8373,13 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B451">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C451" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D451" t="b">
         <v>1</v>
@@ -8354,7 +8396,7 @@
         <v>2010</v>
       </c>
       <c r="C452" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D452" t="b">
         <v>1</v>
@@ -8371,7 +8413,7 @@
         <v>2010</v>
       </c>
       <c r="C453" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D453" t="b">
         <v>1</v>
@@ -8385,10 +8427,10 @@
         <v>45</v>
       </c>
       <c r="B454">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C454" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D454" t="b">
         <v>1</v>
@@ -8402,10 +8444,10 @@
         <v>45</v>
       </c>
       <c r="B455">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C455" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D455" t="b">
         <v>1</v>
@@ -8422,7 +8464,7 @@
         <v>2014</v>
       </c>
       <c r="C456" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D456" t="b">
         <v>1</v>
@@ -8439,7 +8481,7 @@
         <v>2014</v>
       </c>
       <c r="C457" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D457" t="b">
         <v>1</v>
@@ -8450,36 +8492,36 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B458">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C458" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D458" t="b">
         <v>1</v>
       </c>
       <c r="E458" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B459">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C459" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D459" t="b">
         <v>1</v>
       </c>
       <c r="E459" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.2">
@@ -8487,7 +8529,7 @@
         <v>46</v>
       </c>
       <c r="B460">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C460" t="s">
         <v>6</v>
@@ -8496,7 +8538,7 @@
         <v>1</v>
       </c>
       <c r="E460" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.2">
@@ -8504,7 +8546,7 @@
         <v>46</v>
       </c>
       <c r="B461">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C461" t="s">
         <v>26</v>
@@ -8513,7 +8555,7 @@
         <v>1</v>
       </c>
       <c r="E461" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.2">
@@ -8521,7 +8563,7 @@
         <v>46</v>
       </c>
       <c r="B462">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C462" t="s">
         <v>6</v>
@@ -8530,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="E462" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.2">
@@ -8538,7 +8580,7 @@
         <v>46</v>
       </c>
       <c r="B463">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C463" t="s">
         <v>26</v>
@@ -8547,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="E463" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.2">
@@ -8558,13 +8600,13 @@
         <v>2010</v>
       </c>
       <c r="C464" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D464" t="b">
         <v>1</v>
       </c>
       <c r="E464" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.2">
@@ -8575,13 +8617,13 @@
         <v>2010</v>
       </c>
       <c r="C465" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D465" t="b">
         <v>1</v>
       </c>
       <c r="E465" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.2">
@@ -8589,16 +8631,16 @@
         <v>46</v>
       </c>
       <c r="B466">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C466" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D466" t="b">
         <v>1</v>
       </c>
       <c r="E466" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.2">
@@ -8606,16 +8648,16 @@
         <v>46</v>
       </c>
       <c r="B467">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C467" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D467" t="b">
         <v>1</v>
       </c>
       <c r="E467" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.2">
@@ -8626,7 +8668,7 @@
         <v>2012</v>
       </c>
       <c r="C468" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D468" t="b">
         <v>1</v>
@@ -8643,7 +8685,7 @@
         <v>2012</v>
       </c>
       <c r="C469" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D469" t="b">
         <v>1</v>
@@ -8660,7 +8702,7 @@
         <v>2012</v>
       </c>
       <c r="C470" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D470" t="b">
         <v>1</v>
@@ -8677,7 +8719,7 @@
         <v>2012</v>
       </c>
       <c r="C471" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D471" t="b">
         <v>1</v>
@@ -8691,7 +8733,7 @@
         <v>46</v>
       </c>
       <c r="B472">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C472" t="s">
         <v>6</v>
@@ -8700,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="E472" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.2">
@@ -8708,7 +8750,7 @@
         <v>46</v>
       </c>
       <c r="B473">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C473" t="s">
         <v>26</v>
@@ -8717,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="E473" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.2">
@@ -8725,16 +8767,16 @@
         <v>46</v>
       </c>
       <c r="B474">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C474" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D474" t="b">
         <v>1</v>
       </c>
       <c r="E474" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.2">
@@ -8742,16 +8784,16 @@
         <v>46</v>
       </c>
       <c r="B475">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C475" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D475" t="b">
         <v>1</v>
       </c>
       <c r="E475" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.2">
@@ -8762,7 +8804,7 @@
         <v>2016</v>
       </c>
       <c r="C476" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D476" t="b">
         <v>1</v>
@@ -8779,7 +8821,7 @@
         <v>2016</v>
       </c>
       <c r="C477" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D477" t="b">
         <v>1</v>
@@ -8796,7 +8838,7 @@
         <v>2016</v>
       </c>
       <c r="C478" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D478" t="b">
         <v>1</v>
@@ -8813,7 +8855,7 @@
         <v>2016</v>
       </c>
       <c r="C479" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D479" t="b">
         <v>1</v>
@@ -8827,7 +8869,7 @@
         <v>46</v>
       </c>
       <c r="B480">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C480" t="s">
         <v>6</v>
@@ -8836,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="E480" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.2">
@@ -8844,7 +8886,7 @@
         <v>46</v>
       </c>
       <c r="B481">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C481" t="s">
         <v>26</v>
@@ -8853,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="E481" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.2">
@@ -8861,7 +8903,7 @@
         <v>46</v>
       </c>
       <c r="B482">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C482" t="s">
         <v>6</v>
@@ -8870,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="E482" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.2">
@@ -8878,7 +8920,7 @@
         <v>46</v>
       </c>
       <c r="B483">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C483" t="s">
         <v>26</v>
@@ -8887,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="E483" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.2">
@@ -8895,7 +8937,7 @@
         <v>46</v>
       </c>
       <c r="B484">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C484" t="s">
         <v>6</v>
@@ -8904,7 +8946,7 @@
         <v>1</v>
       </c>
       <c r="E484" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.2">
@@ -8912,7 +8954,7 @@
         <v>46</v>
       </c>
       <c r="B485">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C485" t="s">
         <v>26</v>
@@ -8921,41 +8963,41 @@
         <v>1</v>
       </c>
       <c r="E485" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B486">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C486" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D486" t="b">
         <v>1</v>
       </c>
       <c r="E486" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B487">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C487" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D487" t="b">
         <v>1</v>
       </c>
       <c r="E487" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.2">
@@ -8966,7 +9008,7 @@
         <v>2012</v>
       </c>
       <c r="C488" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D488" t="b">
         <v>1</v>
@@ -8983,7 +9025,7 @@
         <v>2012</v>
       </c>
       <c r="C489" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D489" t="b">
         <v>1</v>
@@ -8997,10 +9039,10 @@
         <v>48</v>
       </c>
       <c r="B490">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C490" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D490" t="b">
         <v>1</v>
@@ -9014,10 +9056,10 @@
         <v>48</v>
       </c>
       <c r="B491">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C491" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D491" t="b">
         <v>1</v>
@@ -9034,7 +9076,7 @@
         <v>2016</v>
       </c>
       <c r="C492" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D492" t="b">
         <v>1</v>
@@ -9051,7 +9093,7 @@
         <v>2016</v>
       </c>
       <c r="C493" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D493" t="b">
         <v>1</v>
@@ -9062,36 +9104,36 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B494">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C494" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D494" t="b">
         <v>1</v>
       </c>
       <c r="E494" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B495">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C495" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D495" t="b">
         <v>1</v>
       </c>
       <c r="E495" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.2">
@@ -9102,13 +9144,13 @@
         <v>2006</v>
       </c>
       <c r="C496" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D496" t="b">
         <v>1</v>
       </c>
       <c r="E496" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.2">
@@ -9119,13 +9161,13 @@
         <v>2006</v>
       </c>
       <c r="C497" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D497" t="b">
         <v>1</v>
       </c>
       <c r="E497" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.2">
@@ -9133,16 +9175,16 @@
         <v>49</v>
       </c>
       <c r="B498">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C498" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D498" t="b">
         <v>1</v>
       </c>
       <c r="E498" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.2">
@@ -9150,16 +9192,16 @@
         <v>49</v>
       </c>
       <c r="B499">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C499" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D499" t="b">
         <v>1</v>
       </c>
       <c r="E499" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.2">
@@ -9170,13 +9212,13 @@
         <v>2010</v>
       </c>
       <c r="C500" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D500" t="b">
         <v>1</v>
       </c>
       <c r="E500" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.2">
@@ -9187,13 +9229,13 @@
         <v>2010</v>
       </c>
       <c r="C501" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D501" t="b">
         <v>1</v>
       </c>
       <c r="E501" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.2">
@@ -9201,16 +9243,16 @@
         <v>49</v>
       </c>
       <c r="B502">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C502" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D502" t="b">
         <v>1</v>
       </c>
       <c r="E502" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.2">
@@ -9218,16 +9260,16 @@
         <v>49</v>
       </c>
       <c r="B503">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C503" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D503" t="b">
         <v>1</v>
       </c>
       <c r="E503" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.2">
@@ -9238,13 +9280,13 @@
         <v>2012</v>
       </c>
       <c r="C504" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D504" t="b">
         <v>1</v>
       </c>
       <c r="E504" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.2">
@@ -9255,13 +9297,13 @@
         <v>2012</v>
       </c>
       <c r="C505" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D505" t="b">
         <v>1</v>
       </c>
       <c r="E505" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.2">
@@ -9269,16 +9311,16 @@
         <v>49</v>
       </c>
       <c r="B506">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C506" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D506" t="b">
         <v>1</v>
       </c>
       <c r="E506" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.2">
@@ -9286,16 +9328,16 @@
         <v>49</v>
       </c>
       <c r="B507">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C507" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D507" t="b">
         <v>1</v>
       </c>
       <c r="E507" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.2">
@@ -9306,13 +9348,13 @@
         <v>2014</v>
       </c>
       <c r="C508" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D508" t="b">
         <v>1</v>
       </c>
       <c r="E508" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.2">
@@ -9323,13 +9365,13 @@
         <v>2014</v>
       </c>
       <c r="C509" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D509" t="b">
         <v>1</v>
       </c>
       <c r="E509" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.2">
@@ -9337,16 +9379,16 @@
         <v>49</v>
       </c>
       <c r="B510">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C510" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D510" t="b">
         <v>1</v>
       </c>
       <c r="E510" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.2">
@@ -9354,16 +9396,16 @@
         <v>49</v>
       </c>
       <c r="B511">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C511" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D511" t="b">
         <v>1</v>
       </c>
       <c r="E511" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.2">
@@ -9374,13 +9416,13 @@
         <v>2016</v>
       </c>
       <c r="C512" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D512" t="b">
         <v>1</v>
       </c>
       <c r="E512" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.2">
@@ -9391,24 +9433,24 @@
         <v>2016</v>
       </c>
       <c r="C513" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D513" t="b">
         <v>1</v>
       </c>
       <c r="E513" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B514">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C514" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D514" t="b">
         <v>1</v>
@@ -9419,13 +9461,13 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B515">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C515" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D515" t="b">
         <v>1</v>
@@ -9442,7 +9484,7 @@
         <v>2008</v>
       </c>
       <c r="C516" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D516" t="b">
         <v>1</v>
@@ -9459,7 +9501,7 @@
         <v>2008</v>
       </c>
       <c r="C517" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D517" t="b">
         <v>1</v>
@@ -9473,16 +9515,16 @@
         <v>50</v>
       </c>
       <c r="B518">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C518" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D518" t="b">
         <v>1</v>
       </c>
       <c r="E518" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.2">
@@ -9490,16 +9532,16 @@
         <v>50</v>
       </c>
       <c r="B519">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C519" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D519" t="b">
         <v>1</v>
       </c>
       <c r="E519" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.2">
@@ -9510,7 +9552,7 @@
         <v>2010</v>
       </c>
       <c r="C520" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D520" t="b">
         <v>1</v>
@@ -9527,7 +9569,7 @@
         <v>2010</v>
       </c>
       <c r="C521" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D521" t="b">
         <v>1</v>
@@ -9544,13 +9586,13 @@
         <v>2010</v>
       </c>
       <c r="C522" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D522" t="b">
         <v>1</v>
       </c>
       <c r="E522" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.2">
@@ -9561,13 +9603,13 @@
         <v>2010</v>
       </c>
       <c r="C523" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D523" t="b">
         <v>1</v>
       </c>
       <c r="E523" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.2">
@@ -9578,7 +9620,7 @@
         <v>2010</v>
       </c>
       <c r="C524" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D524" t="b">
         <v>1</v>
@@ -9595,7 +9637,7 @@
         <v>2010</v>
       </c>
       <c r="C525" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D525" t="b">
         <v>1</v>
@@ -9609,16 +9651,16 @@
         <v>50</v>
       </c>
       <c r="B526">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C526" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D526" t="b">
         <v>1</v>
       </c>
       <c r="E526" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.2">
@@ -9626,16 +9668,16 @@
         <v>50</v>
       </c>
       <c r="B527">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C527" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D527" t="b">
         <v>1</v>
       </c>
       <c r="E527" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.2">
@@ -9646,7 +9688,7 @@
         <v>2012</v>
       </c>
       <c r="C528" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D528" t="b">
         <v>1</v>
@@ -9663,7 +9705,7 @@
         <v>2012</v>
       </c>
       <c r="C529" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D529" t="b">
         <v>1</v>
@@ -9680,13 +9722,13 @@
         <v>2012</v>
       </c>
       <c r="C530" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D530" t="b">
         <v>1</v>
       </c>
       <c r="E530" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.2">
@@ -9697,13 +9739,13 @@
         <v>2012</v>
       </c>
       <c r="C531" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D531" t="b">
         <v>1</v>
       </c>
       <c r="E531" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.2">
@@ -9714,7 +9756,7 @@
         <v>2012</v>
       </c>
       <c r="C532" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D532" t="b">
         <v>1</v>
@@ -9731,7 +9773,7 @@
         <v>2012</v>
       </c>
       <c r="C533" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D533" t="b">
         <v>1</v>
@@ -9745,16 +9787,16 @@
         <v>50</v>
       </c>
       <c r="B534">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C534" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D534" t="b">
         <v>1</v>
       </c>
       <c r="E534" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.2">
@@ -9762,16 +9804,16 @@
         <v>50</v>
       </c>
       <c r="B535">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C535" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D535" t="b">
         <v>1</v>
       </c>
       <c r="E535" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.2">
@@ -9782,7 +9824,7 @@
         <v>2014</v>
       </c>
       <c r="C536" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D536" t="b">
         <v>1</v>
@@ -9799,7 +9841,7 @@
         <v>2014</v>
       </c>
       <c r="C537" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D537" t="b">
         <v>1</v>
@@ -9816,13 +9858,13 @@
         <v>2014</v>
       </c>
       <c r="C538" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D538" t="b">
         <v>1</v>
       </c>
       <c r="E538" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.2">
@@ -9833,13 +9875,13 @@
         <v>2014</v>
       </c>
       <c r="C539" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D539" t="b">
         <v>1</v>
       </c>
       <c r="E539" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.2">
@@ -9850,7 +9892,7 @@
         <v>2014</v>
       </c>
       <c r="C540" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D540" t="b">
         <v>1</v>
@@ -9867,7 +9909,7 @@
         <v>2014</v>
       </c>
       <c r="C541" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D541" t="b">
         <v>1</v>
@@ -9881,16 +9923,16 @@
         <v>50</v>
       </c>
       <c r="B542">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C542" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D542" t="b">
         <v>1</v>
       </c>
       <c r="E542" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.2">
@@ -9898,16 +9940,16 @@
         <v>50</v>
       </c>
       <c r="B543">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C543" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D543" t="b">
         <v>1</v>
       </c>
       <c r="E543" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.2">
@@ -9918,7 +9960,7 @@
         <v>2016</v>
       </c>
       <c r="C544" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D544" t="b">
         <v>1</v>
@@ -9935,7 +9977,7 @@
         <v>2016</v>
       </c>
       <c r="C545" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D545" t="b">
         <v>1</v>
@@ -9952,13 +9994,13 @@
         <v>2016</v>
       </c>
       <c r="C546" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D546" t="b">
         <v>1</v>
       </c>
       <c r="E546" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.2">
@@ -9969,13 +10011,13 @@
         <v>2016</v>
       </c>
       <c r="C547" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D547" t="b">
         <v>1</v>
       </c>
       <c r="E547" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.2">
@@ -9986,7 +10028,7 @@
         <v>2016</v>
       </c>
       <c r="C548" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D548" t="b">
         <v>1</v>
@@ -10003,7 +10045,7 @@
         <v>2016</v>
       </c>
       <c r="C549" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D549" t="b">
         <v>1</v>
@@ -10014,10 +10056,10 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B550">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C550" t="s">
         <v>8</v>
@@ -10031,10 +10073,10 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B551">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C551" t="s">
         <v>27</v>
@@ -10051,10 +10093,10 @@
         <v>51</v>
       </c>
       <c r="B552">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C552" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D552" t="b">
         <v>1</v>
@@ -10068,10 +10110,10 @@
         <v>51</v>
       </c>
       <c r="B553">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C553" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D553" t="b">
         <v>1</v>
@@ -10088,7 +10130,7 @@
         <v>2012</v>
       </c>
       <c r="C554" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D554" t="b">
         <v>1</v>
@@ -10105,7 +10147,7 @@
         <v>2012</v>
       </c>
       <c r="C555" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D555" t="b">
         <v>1</v>
@@ -10119,10 +10161,10 @@
         <v>51</v>
       </c>
       <c r="B556">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C556" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D556" t="b">
         <v>1</v>
@@ -10136,10 +10178,10 @@
         <v>51</v>
       </c>
       <c r="B557">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C557" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D557" t="b">
         <v>1</v>
@@ -10153,10 +10195,10 @@
         <v>51</v>
       </c>
       <c r="B558">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C558" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D558" t="b">
         <v>1</v>
@@ -10170,10 +10212,10 @@
         <v>51</v>
       </c>
       <c r="B559">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C559" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D559" t="b">
         <v>1</v>
@@ -10187,10 +10229,10 @@
         <v>51</v>
       </c>
       <c r="B560">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C560" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D560" t="b">
         <v>1</v>
@@ -10204,10 +10246,10 @@
         <v>51</v>
       </c>
       <c r="B561">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C561" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D561" t="b">
         <v>1</v>
@@ -10221,7 +10263,7 @@
         <v>51</v>
       </c>
       <c r="B562">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C562" t="s">
         <v>8</v>
@@ -10238,7 +10280,7 @@
         <v>51</v>
       </c>
       <c r="B563">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C563" t="s">
         <v>27</v>
@@ -10252,36 +10294,36 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B564">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C564" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D564" t="b">
         <v>1</v>
       </c>
       <c r="E564" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B565">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C565" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D565" t="b">
         <v>1</v>
       </c>
       <c r="E565" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.2">
@@ -10289,7 +10331,7 @@
         <v>52</v>
       </c>
       <c r="B566">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C566" t="s">
         <v>10</v>
@@ -10306,7 +10348,7 @@
         <v>52</v>
       </c>
       <c r="B567">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C567" t="s">
         <v>13</v>
@@ -10323,16 +10365,16 @@
         <v>52</v>
       </c>
       <c r="B568">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C568" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D568" t="b">
         <v>1</v>
       </c>
       <c r="E568" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.2">
@@ -10340,16 +10382,16 @@
         <v>52</v>
       </c>
       <c r="B569">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C569" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D569" t="b">
         <v>1</v>
       </c>
       <c r="E569" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.2">
@@ -10360,13 +10402,13 @@
         <v>2012</v>
       </c>
       <c r="C570" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D570" t="b">
         <v>1</v>
       </c>
       <c r="E570" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.2">
@@ -10377,13 +10419,13 @@
         <v>2012</v>
       </c>
       <c r="C571" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D571" t="b">
         <v>1</v>
       </c>
       <c r="E571" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.2">
@@ -10391,7 +10433,7 @@
         <v>52</v>
       </c>
       <c r="B572">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C572" t="s">
         <v>10</v>
@@ -10408,7 +10450,7 @@
         <v>52</v>
       </c>
       <c r="B573">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C573" t="s">
         <v>13</v>
@@ -10425,16 +10467,16 @@
         <v>52</v>
       </c>
       <c r="B574">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C574" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D574" t="b">
         <v>1</v>
       </c>
       <c r="E574" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.2">
@@ -10442,16 +10484,16 @@
         <v>52</v>
       </c>
       <c r="B575">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C575" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D575" t="b">
         <v>1</v>
       </c>
       <c r="E575" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.2">
@@ -10462,13 +10504,13 @@
         <v>2016</v>
       </c>
       <c r="C576" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D576" t="b">
         <v>1</v>
       </c>
       <c r="E576" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.2">
@@ -10479,13 +10521,13 @@
         <v>2016</v>
       </c>
       <c r="C577" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D577" t="b">
         <v>1</v>
       </c>
       <c r="E577" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.2">
@@ -10493,7 +10535,7 @@
         <v>52</v>
       </c>
       <c r="B578">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C578" t="s">
         <v>10</v>
@@ -10510,7 +10552,7 @@
         <v>52</v>
       </c>
       <c r="B579">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C579" t="s">
         <v>13</v>
@@ -10527,16 +10569,16 @@
         <v>52</v>
       </c>
       <c r="B580">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C580" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="D580" t="b">
         <v>1</v>
       </c>
       <c r="E580" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.2">
@@ -10544,16 +10586,16 @@
         <v>52</v>
       </c>
       <c r="B581">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="C581" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D581" t="b">
         <v>1</v>
       </c>
       <c r="E581" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.2">
@@ -10561,7 +10603,7 @@
         <v>52</v>
       </c>
       <c r="B582">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C582" t="s">
         <v>81</v>
@@ -10578,7 +10620,7 @@
         <v>52</v>
       </c>
       <c r="B583">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C583" t="s">
         <v>83</v>
@@ -10598,7 +10640,7 @@
         <v>2008</v>
       </c>
       <c r="C584" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D584" t="b">
         <v>1</v>
@@ -10615,7 +10657,7 @@
         <v>2008</v>
       </c>
       <c r="C585" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D585" t="b">
         <v>1</v>
@@ -10629,7 +10671,7 @@
         <v>52</v>
       </c>
       <c r="B586">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C586" t="s">
         <v>8</v>
@@ -10646,7 +10688,7 @@
         <v>52</v>
       </c>
       <c r="B587">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C587" t="s">
         <v>27</v>
@@ -10663,10 +10705,10 @@
         <v>52</v>
       </c>
       <c r="B588">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C588" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="D588" t="b">
         <v>1</v>
@@ -10680,10 +10722,10 @@
         <v>52</v>
       </c>
       <c r="B589">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C589" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D589" t="b">
         <v>1</v>
@@ -10700,7 +10742,7 @@
         <v>2012</v>
       </c>
       <c r="C590" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D590" t="b">
         <v>1</v>
@@ -10717,7 +10759,7 @@
         <v>2012</v>
       </c>
       <c r="C591" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D591" t="b">
         <v>1</v>
@@ -10731,10 +10773,10 @@
         <v>52</v>
       </c>
       <c r="B592">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C592" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="D592" t="b">
         <v>1</v>
@@ -10748,10 +10790,10 @@
         <v>52</v>
       </c>
       <c r="B593">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C593" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D593" t="b">
         <v>1</v>
@@ -10768,7 +10810,7 @@
         <v>2014</v>
       </c>
       <c r="C594" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D594" t="b">
         <v>1</v>
@@ -10785,7 +10827,7 @@
         <v>2014</v>
       </c>
       <c r="C595" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D595" t="b">
         <v>1</v>
@@ -10799,10 +10841,10 @@
         <v>52</v>
       </c>
       <c r="B596">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C596" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="D596" t="b">
         <v>1</v>
@@ -10816,10 +10858,10 @@
         <v>52</v>
       </c>
       <c r="B597">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C597" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="D597" t="b">
         <v>1</v>
@@ -10836,7 +10878,7 @@
         <v>2016</v>
       </c>
       <c r="C598" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D598" t="b">
         <v>1</v>
@@ -10853,7 +10895,7 @@
         <v>2016</v>
       </c>
       <c r="C599" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D599" t="b">
         <v>1</v>
@@ -10867,7 +10909,7 @@
         <v>52</v>
       </c>
       <c r="B600">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C600" t="s">
         <v>8</v>
@@ -10884,7 +10926,7 @@
         <v>52</v>
       </c>
       <c r="B601">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C601" t="s">
         <v>27</v>
@@ -10901,7 +10943,7 @@
         <v>52</v>
       </c>
       <c r="B602">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C602" t="s">
         <v>8</v>
@@ -10918,7 +10960,7 @@
         <v>52</v>
       </c>
       <c r="B603">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C603" t="s">
         <v>27</v>
@@ -10935,7 +10977,7 @@
         <v>52</v>
       </c>
       <c r="B604">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C604" t="s">
         <v>8</v>
@@ -10952,7 +10994,7 @@
         <v>52</v>
       </c>
       <c r="B605">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C605" t="s">
         <v>27</v>
@@ -10966,36 +11008,36 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B606">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C606" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D606" t="b">
         <v>1</v>
       </c>
       <c r="E606" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B607">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C607" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D607" t="b">
         <v>1</v>
       </c>
       <c r="E607" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.2">
@@ -11006,7 +11048,7 @@
         <v>2010</v>
       </c>
       <c r="C608" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D608" t="b">
         <v>1</v>
@@ -11023,7 +11065,7 @@
         <v>2010</v>
       </c>
       <c r="C609" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D609" t="b">
         <v>1</v>
@@ -11037,10 +11079,10 @@
         <v>53</v>
       </c>
       <c r="B610">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C610" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D610" t="b">
         <v>1</v>
@@ -11054,10 +11096,10 @@
         <v>53</v>
       </c>
       <c r="B611">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C611" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D611" t="b">
         <v>1</v>
@@ -11071,10 +11113,10 @@
         <v>53</v>
       </c>
       <c r="B612">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C612" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D612" t="b">
         <v>1</v>
@@ -11088,10 +11130,10 @@
         <v>53</v>
       </c>
       <c r="B613">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C613" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D613" t="b">
         <v>1</v>
@@ -11108,7 +11150,7 @@
         <v>2014</v>
       </c>
       <c r="C614" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D614" t="b">
         <v>1</v>
@@ -11125,7 +11167,7 @@
         <v>2014</v>
       </c>
       <c r="C615" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D615" t="b">
         <v>1</v>
@@ -11136,13 +11178,13 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B616">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C616" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D616" t="b">
         <v>1</v>
@@ -11153,13 +11195,13 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B617">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C617" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D617" t="b">
         <v>1</v>
@@ -11176,7 +11218,7 @@
         <v>2012</v>
       </c>
       <c r="C618" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D618" t="b">
         <v>1</v>
@@ -11193,7 +11235,7 @@
         <v>2012</v>
       </c>
       <c r="C619" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D619" t="b">
         <v>1</v>
@@ -11207,10 +11249,10 @@
         <v>54</v>
       </c>
       <c r="B620">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C620" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D620" t="b">
         <v>1</v>
@@ -11224,10 +11266,10 @@
         <v>54</v>
       </c>
       <c r="B621">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C621" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D621" t="b">
         <v>1</v>
@@ -11244,7 +11286,7 @@
         <v>2016</v>
       </c>
       <c r="C622" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D622" t="b">
         <v>1</v>
@@ -11261,7 +11303,7 @@
         <v>2016</v>
       </c>
       <c r="C623" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D623" t="b">
         <v>1</v>
@@ -11272,13 +11314,13 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B624">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C624" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D624" t="b">
         <v>1</v>
@@ -11289,13 +11331,13 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B625">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C625" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D625" t="b">
         <v>1</v>
@@ -11312,7 +11354,7 @@
         <v>2012</v>
       </c>
       <c r="C626" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D626" t="b">
         <v>1</v>
@@ -11329,7 +11371,7 @@
         <v>2012</v>
       </c>
       <c r="C627" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D627" t="b">
         <v>1</v>
@@ -11343,10 +11385,10 @@
         <v>55</v>
       </c>
       <c r="B628">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C628" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D628" t="b">
         <v>1</v>
@@ -11360,10 +11402,10 @@
         <v>55</v>
       </c>
       <c r="B629">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C629" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D629" t="b">
         <v>1</v>
@@ -11380,7 +11422,7 @@
         <v>2016</v>
       </c>
       <c r="C630" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D630" t="b">
         <v>1</v>
@@ -11397,7 +11439,7 @@
         <v>2016</v>
       </c>
       <c r="C631" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D631" t="b">
         <v>1</v>
@@ -11408,10 +11450,10 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B632">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C632" t="s">
         <v>10</v>
@@ -11420,15 +11462,15 @@
         <v>1</v>
       </c>
       <c r="E632" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B633">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C633" t="s">
         <v>13</v>
@@ -11437,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="E633" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.2">
@@ -11445,16 +11487,16 @@
         <v>56</v>
       </c>
       <c r="B634">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C634" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D634" t="b">
         <v>1</v>
       </c>
       <c r="E634" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.2">
@@ -11462,16 +11504,16 @@
         <v>56</v>
       </c>
       <c r="B635">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C635" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D635" t="b">
         <v>1</v>
       </c>
       <c r="E635" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.2">
@@ -11479,16 +11521,16 @@
         <v>56</v>
       </c>
       <c r="B636">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C636" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D636" t="b">
         <v>1</v>
       </c>
       <c r="E636" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.2">
@@ -11496,16 +11538,16 @@
         <v>56</v>
       </c>
       <c r="B637">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C637" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D637" t="b">
         <v>1</v>
       </c>
       <c r="E637" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.2">
@@ -11513,16 +11555,16 @@
         <v>56</v>
       </c>
       <c r="B638">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C638" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D638" t="b">
         <v>1</v>
       </c>
       <c r="E638" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.2">
@@ -11530,16 +11572,16 @@
         <v>56</v>
       </c>
       <c r="B639">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C639" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D639" t="b">
         <v>1</v>
       </c>
       <c r="E639" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.2">
@@ -11550,7 +11592,7 @@
         <v>2012</v>
       </c>
       <c r="C640" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D640" t="b">
         <v>1</v>
@@ -11567,7 +11609,7 @@
         <v>2012</v>
       </c>
       <c r="C641" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D641" t="b">
         <v>1</v>
@@ -11581,16 +11623,16 @@
         <v>56</v>
       </c>
       <c r="B642">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C642" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D642" t="b">
         <v>1</v>
       </c>
       <c r="E642" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.2">
@@ -11598,16 +11640,16 @@
         <v>56</v>
       </c>
       <c r="B643">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C643" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D643" t="b">
         <v>1</v>
       </c>
       <c r="E643" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.2">
@@ -11618,13 +11660,13 @@
         <v>2014</v>
       </c>
       <c r="C644" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D644" t="b">
         <v>1</v>
       </c>
       <c r="E644" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.2">
@@ -11635,13 +11677,13 @@
         <v>2014</v>
       </c>
       <c r="C645" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D645" t="b">
         <v>1</v>
       </c>
       <c r="E645" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.2">
@@ -11649,16 +11691,16 @@
         <v>56</v>
       </c>
       <c r="B646">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C646" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D646" t="b">
         <v>1</v>
       </c>
       <c r="E646" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.2">
@@ -11666,16 +11708,16 @@
         <v>56</v>
       </c>
       <c r="B647">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C647" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D647" t="b">
         <v>1</v>
       </c>
       <c r="E647" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.2">
@@ -11686,7 +11728,7 @@
         <v>2016</v>
       </c>
       <c r="C648" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D648" t="b">
         <v>1</v>
@@ -11703,7 +11745,7 @@
         <v>2016</v>
       </c>
       <c r="C649" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D649" t="b">
         <v>1</v>
@@ -11714,13 +11756,13 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B650">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C650" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D650" t="b">
         <v>1</v>
@@ -11731,13 +11773,13 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B651">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C651" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D651" t="b">
         <v>1</v>
@@ -11754,7 +11796,7 @@
         <v>2006</v>
       </c>
       <c r="C652" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D652" t="b">
         <v>1</v>
@@ -11771,7 +11813,7 @@
         <v>2006</v>
       </c>
       <c r="C653" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D653" t="b">
         <v>1</v>
@@ -11785,10 +11827,10 @@
         <v>58</v>
       </c>
       <c r="B654">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C654" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D654" t="b">
         <v>1</v>
@@ -11802,10 +11844,10 @@
         <v>58</v>
       </c>
       <c r="B655">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C655" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D655" t="b">
         <v>1</v>
@@ -11822,7 +11864,7 @@
         <v>2010</v>
       </c>
       <c r="C656" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D656" t="b">
         <v>1</v>
@@ -11839,7 +11881,7 @@
         <v>2010</v>
       </c>
       <c r="C657" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D657" t="b">
         <v>1</v>
@@ -11853,10 +11895,10 @@
         <v>58</v>
       </c>
       <c r="B658">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C658" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D658" t="b">
         <v>1</v>
@@ -11870,10 +11912,10 @@
         <v>58</v>
       </c>
       <c r="B659">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C659" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D659" t="b">
         <v>1</v>
@@ -11890,7 +11932,7 @@
         <v>2014</v>
       </c>
       <c r="C660" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D660" t="b">
         <v>1</v>
@@ -11907,7 +11949,7 @@
         <v>2014</v>
       </c>
       <c r="C661" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D661" t="b">
         <v>1</v>
@@ -11918,13 +11960,13 @@
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B662">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C662" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D662" t="b">
         <v>1</v>
@@ -11935,13 +11977,13 @@
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B663">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C663" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D663" t="b">
         <v>1</v>
@@ -11958,13 +12000,13 @@
         <v>2006</v>
       </c>
       <c r="C664" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D664" t="b">
         <v>1</v>
       </c>
       <c r="E664" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="665" spans="1:5" x14ac:dyDescent="0.2">
@@ -11975,13 +12017,13 @@
         <v>2006</v>
       </c>
       <c r="C665" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D665" t="b">
         <v>1</v>
       </c>
       <c r="E665" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="666" spans="1:5" x14ac:dyDescent="0.2">
@@ -11989,16 +12031,16 @@
         <v>59</v>
       </c>
       <c r="B666">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C666" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D666" t="b">
         <v>1</v>
       </c>
       <c r="E666" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="667" spans="1:5" x14ac:dyDescent="0.2">
@@ -12006,16 +12048,16 @@
         <v>59</v>
       </c>
       <c r="B667">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C667" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D667" t="b">
         <v>1</v>
       </c>
       <c r="E667" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="668" spans="1:5" x14ac:dyDescent="0.2">
@@ -12026,13 +12068,13 @@
         <v>2010</v>
       </c>
       <c r="C668" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D668" t="b">
         <v>1</v>
       </c>
       <c r="E668" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="669" spans="1:5" x14ac:dyDescent="0.2">
@@ -12043,13 +12085,13 @@
         <v>2010</v>
       </c>
       <c r="C669" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D669" t="b">
         <v>1</v>
       </c>
       <c r="E669" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="670" spans="1:5" x14ac:dyDescent="0.2">
@@ -12057,7 +12099,7 @@
         <v>59</v>
       </c>
       <c r="B670">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C670" t="s">
         <v>10</v>
@@ -12074,7 +12116,7 @@
         <v>59</v>
       </c>
       <c r="B671">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C671" t="s">
         <v>13</v>
@@ -12091,16 +12133,16 @@
         <v>59</v>
       </c>
       <c r="B672">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C672" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D672" t="b">
         <v>1</v>
       </c>
       <c r="E672" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="673" spans="1:5" x14ac:dyDescent="0.2">
@@ -12108,16 +12150,16 @@
         <v>59</v>
       </c>
       <c r="B673">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C673" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D673" t="b">
         <v>1</v>
       </c>
       <c r="E673" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="674" spans="1:5" x14ac:dyDescent="0.2">
@@ -12128,13 +12170,13 @@
         <v>2014</v>
       </c>
       <c r="C674" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D674" t="b">
         <v>1</v>
       </c>
       <c r="E674" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="675" spans="1:5" x14ac:dyDescent="0.2">
@@ -12145,13 +12187,13 @@
         <v>2014</v>
       </c>
       <c r="C675" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D675" t="b">
         <v>1</v>
       </c>
       <c r="E675" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="676" spans="1:5" x14ac:dyDescent="0.2">
@@ -12159,7 +12201,7 @@
         <v>59</v>
       </c>
       <c r="B676">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C676" t="s">
         <v>10</v>
@@ -12176,7 +12218,7 @@
         <v>59</v>
       </c>
       <c r="B677">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C677" t="s">
         <v>13</v>
@@ -12190,36 +12232,36 @@
     </row>
     <row r="678" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B678">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C678" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D678" t="b">
         <v>1</v>
       </c>
       <c r="E678" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="679" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B679">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C679" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D679" t="b">
         <v>1</v>
       </c>
       <c r="E679" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="680" spans="1:5" x14ac:dyDescent="0.2">
@@ -12230,7 +12272,7 @@
         <v>2012</v>
       </c>
       <c r="C680" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D680" t="b">
         <v>1</v>
@@ -12247,7 +12289,7 @@
         <v>2012</v>
       </c>
       <c r="C681" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D681" t="b">
         <v>1</v>
@@ -12261,10 +12303,10 @@
         <v>60</v>
       </c>
       <c r="B682">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C682" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D682" t="b">
         <v>1</v>
@@ -12278,10 +12320,10 @@
         <v>60</v>
       </c>
       <c r="B683">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C683" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D683" t="b">
         <v>1</v>
@@ -12298,7 +12340,7 @@
         <v>2016</v>
       </c>
       <c r="C684" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D684" t="b">
         <v>1</v>
@@ -12315,7 +12357,7 @@
         <v>2016</v>
       </c>
       <c r="C685" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D685" t="b">
         <v>1</v>
@@ -12326,13 +12368,13 @@
     </row>
     <row r="686" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B686">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C686" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D686" t="b">
         <v>1</v>
@@ -12343,13 +12385,13 @@
     </row>
     <row r="687" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B687">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C687" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D687" t="b">
         <v>1</v>
@@ -12363,7 +12405,7 @@
         <v>61</v>
       </c>
       <c r="B688">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C688" t="s">
         <v>8</v>
@@ -12380,7 +12422,7 @@
         <v>61</v>
       </c>
       <c r="B689">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C689" t="s">
         <v>27</v>
@@ -12397,10 +12439,10 @@
         <v>61</v>
       </c>
       <c r="B690">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C690" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D690" t="b">
         <v>1</v>
@@ -12414,10 +12456,10 @@
         <v>61</v>
       </c>
       <c r="B691">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C691" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D691" t="b">
         <v>1</v>
@@ -12434,7 +12476,7 @@
         <v>2012</v>
       </c>
       <c r="C692" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D692" t="b">
         <v>1</v>
@@ -12451,7 +12493,7 @@
         <v>2012</v>
       </c>
       <c r="C693" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D693" t="b">
         <v>1</v>
@@ -12468,13 +12510,13 @@
         <v>2012</v>
       </c>
       <c r="C694" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D694" t="b">
         <v>1</v>
       </c>
       <c r="E694" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.2">
@@ -12485,13 +12527,13 @@
         <v>2012</v>
       </c>
       <c r="C695" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D695" t="b">
         <v>1</v>
       </c>
       <c r="E695" t="s">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.2">
@@ -12499,16 +12541,16 @@
         <v>61</v>
       </c>
       <c r="B696">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C696" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D696" t="b">
         <v>1</v>
       </c>
       <c r="E696" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.2">
@@ -12516,16 +12558,16 @@
         <v>61</v>
       </c>
       <c r="B697">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C697" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D697" t="b">
         <v>1</v>
       </c>
       <c r="E697" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.2">
@@ -12536,7 +12578,7 @@
         <v>2016</v>
       </c>
       <c r="C698" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D698" t="b">
         <v>1</v>
@@ -12553,7 +12595,7 @@
         <v>2016</v>
       </c>
       <c r="C699" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D699" t="b">
         <v>1</v>
@@ -12564,13 +12606,13 @@
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B700">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C700" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D700" t="b">
         <v>1</v>
@@ -12581,13 +12623,13 @@
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B701">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C701" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D701" t="b">
         <v>1</v>
@@ -12604,7 +12646,7 @@
         <v>2012</v>
       </c>
       <c r="C702" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D702" t="b">
         <v>1</v>
@@ -12621,7 +12663,7 @@
         <v>2012</v>
       </c>
       <c r="C703" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D703" t="b">
         <v>1</v>
@@ -12635,10 +12677,10 @@
         <v>62</v>
       </c>
       <c r="B704">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C704" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D704" t="b">
         <v>1</v>
@@ -12652,10 +12694,10 @@
         <v>62</v>
       </c>
       <c r="B705">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C705" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D705" t="b">
         <v>1</v>
@@ -12672,7 +12714,7 @@
         <v>2016</v>
       </c>
       <c r="C706" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D706" t="b">
         <v>1</v>
@@ -12689,7 +12731,7 @@
         <v>2016</v>
       </c>
       <c r="C707" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D707" t="b">
         <v>1</v>
@@ -12700,36 +12742,36 @@
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B708">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C708" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D708" t="b">
         <v>1</v>
       </c>
       <c r="E708" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B709">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C709" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D709" t="b">
         <v>1</v>
       </c>
       <c r="E709" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.2">
@@ -12740,7 +12782,7 @@
         <v>2006</v>
       </c>
       <c r="C710" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D710" t="b">
         <v>1</v>
@@ -12757,7 +12799,7 @@
         <v>2006</v>
       </c>
       <c r="C711" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D711" t="b">
         <v>1</v>
@@ -12771,10 +12813,10 @@
         <v>63</v>
       </c>
       <c r="B712">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C712" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D712" t="b">
         <v>1</v>
@@ -12788,10 +12830,10 @@
         <v>63</v>
       </c>
       <c r="B713">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C713" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D713" t="b">
         <v>1</v>
@@ -12808,7 +12850,7 @@
         <v>2010</v>
       </c>
       <c r="C714" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D714" t="b">
         <v>1</v>
@@ -12825,7 +12867,7 @@
         <v>2010</v>
       </c>
       <c r="C715" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D715" t="b">
         <v>1</v>
@@ -12839,10 +12881,10 @@
         <v>63</v>
       </c>
       <c r="B716">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C716" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D716" t="b">
         <v>1</v>
@@ -12856,10 +12898,10 @@
         <v>63</v>
       </c>
       <c r="B717">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C717" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D717" t="b">
         <v>1</v>
@@ -12876,7 +12918,7 @@
         <v>2012</v>
       </c>
       <c r="C718" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D718" t="b">
         <v>1</v>
@@ -12893,7 +12935,7 @@
         <v>2012</v>
       </c>
       <c r="C719" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D719" t="b">
         <v>1</v>
@@ -12907,10 +12949,10 @@
         <v>63</v>
       </c>
       <c r="B720">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C720" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D720" t="b">
         <v>1</v>
@@ -12924,10 +12966,10 @@
         <v>63</v>
       </c>
       <c r="B721">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C721" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D721" t="b">
         <v>1</v>
@@ -12944,7 +12986,7 @@
         <v>2014</v>
       </c>
       <c r="C722" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D722" t="b">
         <v>1</v>
@@ -12961,7 +13003,7 @@
         <v>2014</v>
       </c>
       <c r="C723" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D723" t="b">
         <v>1</v>
@@ -12975,10 +13017,10 @@
         <v>63</v>
       </c>
       <c r="B724">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C724" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D724" t="b">
         <v>1</v>
@@ -12992,10 +13034,10 @@
         <v>63</v>
       </c>
       <c r="B725">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C725" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D725" t="b">
         <v>1</v>
@@ -13012,7 +13054,7 @@
         <v>2016</v>
       </c>
       <c r="C726" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D726" t="b">
         <v>1</v>
@@ -13029,7 +13071,7 @@
         <v>2016</v>
       </c>
       <c r="C727" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D727" t="b">
         <v>1</v>
@@ -13040,10 +13082,10 @@
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B728">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C728" t="s">
         <v>10</v>
@@ -13057,10 +13099,10 @@
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B729">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C729" t="s">
         <v>13</v>
@@ -13077,7 +13119,7 @@
         <v>64</v>
       </c>
       <c r="B730">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C730" t="s">
         <v>10</v>
@@ -13094,7 +13136,7 @@
         <v>64</v>
       </c>
       <c r="B731">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C731" t="s">
         <v>13</v>
@@ -13111,16 +13153,16 @@
         <v>64</v>
       </c>
       <c r="B732">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C732" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D732" t="b">
         <v>1</v>
       </c>
       <c r="E732" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.2">
@@ -13128,16 +13170,16 @@
         <v>64</v>
       </c>
       <c r="B733">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C733" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D733" t="b">
         <v>1</v>
       </c>
       <c r="E733" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.2">
@@ -13148,7 +13190,7 @@
         <v>2012</v>
       </c>
       <c r="C734" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D734" t="b">
         <v>1</v>
@@ -13165,7 +13207,7 @@
         <v>2012</v>
       </c>
       <c r="C735" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D735" t="b">
         <v>1</v>
@@ -13179,7 +13221,7 @@
         <v>64</v>
       </c>
       <c r="B736">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C736" t="s">
         <v>10</v>
@@ -13188,7 +13230,7 @@
         <v>1</v>
       </c>
       <c r="E736" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="737" spans="1:5" x14ac:dyDescent="0.2">
@@ -13196,7 +13238,7 @@
         <v>64</v>
       </c>
       <c r="B737">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C737" t="s">
         <v>13</v>
@@ -13205,7 +13247,7 @@
         <v>1</v>
       </c>
       <c r="E737" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.2">
@@ -13213,16 +13255,16 @@
         <v>64</v>
       </c>
       <c r="B738">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C738" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D738" t="b">
         <v>1</v>
       </c>
       <c r="E738" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.2">
@@ -13230,16 +13272,16 @@
         <v>64</v>
       </c>
       <c r="B739">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C739" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D739" t="b">
         <v>1</v>
       </c>
       <c r="E739" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="740" spans="1:5" x14ac:dyDescent="0.2">
@@ -13250,7 +13292,7 @@
         <v>2016</v>
       </c>
       <c r="C740" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D740" t="b">
         <v>1</v>
@@ -13267,7 +13309,7 @@
         <v>2016</v>
       </c>
       <c r="C741" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D741" t="b">
         <v>1</v>
@@ -13278,13 +13320,13 @@
     </row>
     <row r="742" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B742">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C742" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D742" t="b">
         <v>1</v>
@@ -13295,13 +13337,13 @@
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B743">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="C743" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D743" t="b">
         <v>1</v>
@@ -13318,13 +13360,13 @@
         <v>2010</v>
       </c>
       <c r="C744" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D744" t="b">
         <v>1</v>
       </c>
       <c r="E744" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="745" spans="1:5" x14ac:dyDescent="0.2">
@@ -13335,13 +13377,13 @@
         <v>2010</v>
       </c>
       <c r="C745" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D745" t="b">
         <v>1</v>
       </c>
       <c r="E745" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.2">
@@ -13349,7 +13391,7 @@
         <v>65</v>
       </c>
       <c r="B746">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C746" t="s">
         <v>10</v>
@@ -13366,7 +13408,7 @@
         <v>65</v>
       </c>
       <c r="B747">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C747" t="s">
         <v>13</v>
@@ -13383,7 +13425,7 @@
         <v>65</v>
       </c>
       <c r="B748">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C748" t="s">
         <v>10</v>
@@ -13400,7 +13442,7 @@
         <v>65</v>
       </c>
       <c r="B749">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C749" t="s">
         <v>13</v>
@@ -13417,7 +13459,7 @@
         <v>65</v>
       </c>
       <c r="B750">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C750" t="s">
         <v>10</v>
@@ -13434,7 +13476,7 @@
         <v>65</v>
       </c>
       <c r="B751">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C751" t="s">
         <v>13</v>
@@ -13451,7 +13493,7 @@
         <v>65</v>
       </c>
       <c r="B752">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C752" t="s">
         <v>10</v>
@@ -13468,7 +13510,7 @@
         <v>65</v>
       </c>
       <c r="B753">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C753" t="s">
         <v>13</v>
@@ -13485,7 +13527,7 @@
         <v>65</v>
       </c>
       <c r="B754">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C754" t="s">
         <v>10</v>
@@ -13502,7 +13544,7 @@
         <v>65</v>
       </c>
       <c r="B755">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C755" t="s">
         <v>13</v>
@@ -13519,7 +13561,7 @@
         <v>65</v>
       </c>
       <c r="B756">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C756" t="s">
         <v>10</v>
@@ -13536,7 +13578,7 @@
         <v>65</v>
       </c>
       <c r="B757">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C757" t="s">
         <v>13</v>
@@ -13550,36 +13592,36 @@
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B758">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C758" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D758" t="b">
         <v>1</v>
       </c>
       <c r="E758" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="759" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B759">
-        <v>2008</v>
+        <v>2022</v>
       </c>
       <c r="C759" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D759" t="b">
         <v>1</v>
       </c>
       <c r="E759" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="760" spans="1:5" x14ac:dyDescent="0.2">
@@ -13590,7 +13632,7 @@
         <v>2008</v>
       </c>
       <c r="C760" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D760" t="b">
         <v>1</v>
@@ -13607,7 +13649,7 @@
         <v>2008</v>
       </c>
       <c r="C761" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D761" t="b">
         <v>1</v>
@@ -13621,10 +13663,10 @@
         <v>66</v>
       </c>
       <c r="B762">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C762" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D762" t="b">
         <v>1</v>
@@ -13638,10 +13680,10 @@
         <v>66</v>
       </c>
       <c r="B763">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C763" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D763" t="b">
         <v>1</v>
@@ -13658,7 +13700,7 @@
         <v>2010</v>
       </c>
       <c r="C764" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D764" t="b">
         <v>1</v>
@@ -13675,7 +13717,7 @@
         <v>2010</v>
       </c>
       <c r="C765" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D765" t="b">
         <v>1</v>
@@ -13692,7 +13734,7 @@
         <v>2010</v>
       </c>
       <c r="C766" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D766" t="b">
         <v>1</v>
@@ -13709,7 +13751,7 @@
         <v>2010</v>
       </c>
       <c r="C767" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D767" t="b">
         <v>1</v>
@@ -13726,7 +13768,7 @@
         <v>2010</v>
       </c>
       <c r="C768" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D768" t="b">
         <v>1</v>
@@ -13743,7 +13785,7 @@
         <v>2010</v>
       </c>
       <c r="C769" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D769" t="b">
         <v>1</v>
@@ -13757,10 +13799,10 @@
         <v>66</v>
       </c>
       <c r="B770">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C770" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D770" t="b">
         <v>1</v>
@@ -13774,10 +13816,10 @@
         <v>66</v>
       </c>
       <c r="B771">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C771" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D771" t="b">
         <v>1</v>
@@ -13794,7 +13836,7 @@
         <v>2012</v>
       </c>
       <c r="C772" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D772" t="b">
         <v>1</v>
@@ -13811,7 +13853,7 @@
         <v>2012</v>
       </c>
       <c r="C773" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D773" t="b">
         <v>1</v>
@@ -13828,7 +13870,7 @@
         <v>2012</v>
       </c>
       <c r="C774" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D774" t="b">
         <v>1</v>
@@ -13845,7 +13887,7 @@
         <v>2012</v>
       </c>
       <c r="C775" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D775" t="b">
         <v>1</v>
@@ -13862,7 +13904,7 @@
         <v>2012</v>
       </c>
       <c r="C776" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D776" t="b">
         <v>1</v>
@@ -13879,7 +13921,7 @@
         <v>2012</v>
       </c>
       <c r="C777" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D777" t="b">
         <v>1</v>
@@ -13893,10 +13935,10 @@
         <v>66</v>
       </c>
       <c r="B778">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C778" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D778" t="b">
         <v>1</v>
@@ -13910,10 +13952,10 @@
         <v>66</v>
       </c>
       <c r="B779">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C779" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D779" t="b">
         <v>1</v>
@@ -13930,7 +13972,7 @@
         <v>2014</v>
       </c>
       <c r="C780" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D780" t="b">
         <v>1</v>
@@ -13947,7 +13989,7 @@
         <v>2014</v>
       </c>
       <c r="C781" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D781" t="b">
         <v>1</v>
@@ -13964,7 +14006,7 @@
         <v>2014</v>
       </c>
       <c r="C782" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D782" t="b">
         <v>1</v>
@@ -13981,7 +14023,7 @@
         <v>2014</v>
       </c>
       <c r="C783" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D783" t="b">
         <v>1</v>
@@ -13998,7 +14040,7 @@
         <v>2014</v>
       </c>
       <c r="C784" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D784" t="b">
         <v>1</v>
@@ -14015,7 +14057,7 @@
         <v>2014</v>
       </c>
       <c r="C785" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D785" t="b">
         <v>1</v>
@@ -14029,10 +14071,10 @@
         <v>66</v>
       </c>
       <c r="B786">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C786" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D786" t="b">
         <v>1</v>
@@ -14046,10 +14088,10 @@
         <v>66</v>
       </c>
       <c r="B787">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C787" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D787" t="b">
         <v>1</v>
@@ -14066,7 +14108,7 @@
         <v>2016</v>
       </c>
       <c r="C788" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D788" t="b">
         <v>1</v>
@@ -14083,7 +14125,7 @@
         <v>2016</v>
       </c>
       <c r="C789" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D789" t="b">
         <v>1</v>
@@ -14100,7 +14142,7 @@
         <v>2016</v>
       </c>
       <c r="C790" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D790" t="b">
         <v>1</v>
@@ -14117,7 +14159,7 @@
         <v>2016</v>
       </c>
       <c r="C791" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D791" t="b">
         <v>1</v>
@@ -14134,7 +14176,7 @@
         <v>2016</v>
       </c>
       <c r="C792" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D792" t="b">
         <v>1</v>
@@ -14151,7 +14193,7 @@
         <v>2016</v>
       </c>
       <c r="C793" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D793" t="b">
         <v>1</v>
@@ -14168,7 +14210,7 @@
         <v>2016</v>
       </c>
       <c r="C794" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D794" t="b">
         <v>1</v>
@@ -14185,7 +14227,7 @@
         <v>2016</v>
       </c>
       <c r="C795" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D795" t="b">
         <v>1</v>
@@ -14199,7 +14241,7 @@
         <v>66</v>
       </c>
       <c r="B796">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C796" t="s">
         <v>8</v>
@@ -14216,7 +14258,7 @@
         <v>66</v>
       </c>
       <c r="B797">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C797" t="s">
         <v>27</v>
@@ -14233,7 +14275,7 @@
         <v>66</v>
       </c>
       <c r="B798">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C798" t="s">
         <v>8</v>
@@ -14250,7 +14292,7 @@
         <v>66</v>
       </c>
       <c r="B799">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C799" t="s">
         <v>27</v>
@@ -14267,7 +14309,7 @@
         <v>66</v>
       </c>
       <c r="B800">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C800" t="s">
         <v>8</v>
@@ -14284,7 +14326,7 @@
         <v>66</v>
       </c>
       <c r="B801">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C801" t="s">
         <v>27</v>
@@ -14298,13 +14340,13 @@
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B802">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C802" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D802" t="b">
         <v>1</v>
@@ -14315,13 +14357,13 @@
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B803">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C803" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D803" t="b">
         <v>1</v>
@@ -14338,7 +14380,7 @@
         <v>2010</v>
       </c>
       <c r="C804" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D804" t="b">
         <v>1</v>
@@ -14355,7 +14397,7 @@
         <v>2010</v>
       </c>
       <c r="C805" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D805" t="b">
         <v>1</v>
@@ -14369,10 +14411,10 @@
         <v>67</v>
       </c>
       <c r="B806">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C806" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D806" t="b">
         <v>1</v>
@@ -14386,10 +14428,10 @@
         <v>67</v>
       </c>
       <c r="B807">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C807" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D807" t="b">
         <v>1</v>
@@ -14406,7 +14448,7 @@
         <v>2014</v>
       </c>
       <c r="C808" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D808" t="b">
         <v>1</v>
@@ -14423,7 +14465,7 @@
         <v>2014</v>
       </c>
       <c r="C809" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D809" t="b">
         <v>1</v>
@@ -14437,10 +14479,10 @@
         <v>67</v>
       </c>
       <c r="B810">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C810" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D810" t="b">
         <v>1</v>
@@ -14454,10 +14496,10 @@
         <v>67</v>
       </c>
       <c r="B811">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C811" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D811" t="b">
         <v>1</v>
@@ -14468,10 +14510,10 @@
     </row>
     <row r="812" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B812">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C812" t="s">
         <v>9</v>
@@ -14485,10 +14527,10 @@
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B813">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C813" t="s">
         <v>14</v>
@@ -14508,7 +14550,7 @@
         <v>2010</v>
       </c>
       <c r="C814" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D814" t="b">
         <v>1</v>
@@ -14525,7 +14567,7 @@
         <v>2010</v>
       </c>
       <c r="C815" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D815" t="b">
         <v>1</v>
@@ -14539,10 +14581,10 @@
         <v>68</v>
       </c>
       <c r="B816">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C816" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D816" t="b">
         <v>1</v>
@@ -14556,10 +14598,10 @@
         <v>68</v>
       </c>
       <c r="B817">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="C817" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D817" t="b">
         <v>1</v>
@@ -14576,7 +14618,7 @@
         <v>2014</v>
       </c>
       <c r="C818" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D818" t="b">
         <v>1</v>
@@ -14593,7 +14635,7 @@
         <v>2014</v>
       </c>
       <c r="C819" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D819" t="b">
         <v>1</v>
@@ -14604,13 +14646,13 @@
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B820">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C820" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D820" t="b">
         <v>1</v>
@@ -14621,13 +14663,13 @@
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B821">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C821" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D821" t="b">
         <v>1</v>
@@ -14644,7 +14686,7 @@
         <v>2012</v>
       </c>
       <c r="C822" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D822" t="b">
         <v>1</v>
@@ -14661,7 +14703,7 @@
         <v>2012</v>
       </c>
       <c r="C823" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D823" t="b">
         <v>1</v>
@@ -14675,10 +14717,10 @@
         <v>69</v>
       </c>
       <c r="B824">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C824" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D824" t="b">
         <v>1</v>
@@ -14692,10 +14734,10 @@
         <v>69</v>
       </c>
       <c r="B825">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C825" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D825" t="b">
         <v>1</v>
@@ -14712,7 +14754,7 @@
         <v>2016</v>
       </c>
       <c r="C826" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D826" t="b">
         <v>1</v>
@@ -14729,7 +14771,7 @@
         <v>2016</v>
       </c>
       <c r="C827" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D827" t="b">
         <v>1</v>
@@ -14740,36 +14782,36 @@
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B828">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C828" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D828" t="b">
         <v>1</v>
       </c>
       <c r="E828" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B829">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="C829" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D829" t="b">
         <v>1</v>
       </c>
       <c r="E829" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.2">
@@ -14777,7 +14819,7 @@
         <v>70</v>
       </c>
       <c r="B830">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C830" t="s">
         <v>9</v>
@@ -14794,7 +14836,7 @@
         <v>70</v>
       </c>
       <c r="B831">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="C831" t="s">
         <v>14</v>
@@ -14811,7 +14853,7 @@
         <v>70</v>
       </c>
       <c r="B832">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C832" t="s">
         <v>9</v>
@@ -14828,7 +14870,7 @@
         <v>70</v>
       </c>
       <c r="B833">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C833" t="s">
         <v>14</v>
@@ -14848,13 +14890,13 @@
         <v>2012</v>
       </c>
       <c r="C834" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D834" t="b">
         <v>1</v>
       </c>
       <c r="E834" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.2">
@@ -14865,13 +14907,13 @@
         <v>2012</v>
       </c>
       <c r="C835" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D835" t="b">
         <v>1</v>
       </c>
       <c r="E835" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.2">
@@ -14879,16 +14921,16 @@
         <v>70</v>
       </c>
       <c r="B836">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C836" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D836" t="b">
         <v>1</v>
       </c>
       <c r="E836" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.2">
@@ -14896,16 +14938,16 @@
         <v>70</v>
       </c>
       <c r="B837">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C837" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D837" t="b">
         <v>1</v>
       </c>
       <c r="E837" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.2">
@@ -14913,7 +14955,7 @@
         <v>70</v>
       </c>
       <c r="B838">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C838" t="s">
         <v>9</v>
@@ -14930,7 +14972,7 @@
         <v>70</v>
       </c>
       <c r="B839">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C839" t="s">
         <v>14</v>
@@ -14950,13 +14992,13 @@
         <v>2016</v>
       </c>
       <c r="C840" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D840" t="b">
         <v>1</v>
       </c>
       <c r="E840" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="841" spans="1:5" x14ac:dyDescent="0.2">
@@ -14967,21 +15009,21 @@
         <v>2016</v>
       </c>
       <c r="C841" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D841" t="b">
         <v>1</v>
       </c>
       <c r="E841" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="842" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B842">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C842" t="s">
         <v>10</v>
@@ -14990,15 +15032,15 @@
         <v>1</v>
       </c>
       <c r="E842" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B843">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C843" t="s">
         <v>13</v>
@@ -15007,46 +15049,46 @@
         <v>1</v>
       </c>
       <c r="E843" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B844">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C844" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D844" t="b">
         <v>1</v>
       </c>
       <c r="E844" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B845">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C845" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D845" t="b">
         <v>1</v>
       </c>
       <c r="E845" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B846">
         <v>2018</v>
@@ -15063,7 +15105,7 @@
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B847">
         <v>2018</v>
@@ -15080,7 +15122,7 @@
     </row>
     <row r="848" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B848">
         <v>2018</v>
@@ -15097,13 +15139,13 @@
     </row>
     <row r="849" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B849">
         <v>2018</v>
       </c>
       <c r="C849" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D849" t="b">
         <v>1</v>
@@ -15114,13 +15156,13 @@
     </row>
     <row r="850" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B850">
         <v>2018</v>
       </c>
       <c r="C850" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D850" t="b">
         <v>1</v>
@@ -15131,13 +15173,13 @@
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="B851">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C851" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D851" t="b">
         <v>1</v>
@@ -15148,10 +15190,10 @@
     </row>
     <row r="852" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="B852">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C852" t="s">
         <v>26</v>
@@ -15165,13 +15207,13 @@
     </row>
     <row r="853" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B853">
         <v>2020</v>
       </c>
       <c r="C853" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D853" t="b">
         <v>1</v>
@@ -15182,13 +15224,13 @@
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B854">
         <v>2020</v>
       </c>
       <c r="C854" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D854" t="b">
         <v>1</v>
@@ -15199,13 +15241,13 @@
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B855">
         <v>2020</v>
       </c>
       <c r="C855" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D855" t="b">
         <v>1</v>
@@ -15216,10 +15258,10 @@
     </row>
     <row r="856" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B856">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C856" t="s">
         <v>27</v>
@@ -15233,10 +15275,10 @@
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="B857">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C857" t="s">
         <v>26</v>
@@ -15250,7 +15292,7 @@
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B858">
         <v>2022</v>
@@ -15267,13 +15309,13 @@
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B859">
         <v>2022</v>
       </c>
       <c r="C859" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D859" t="b">
         <v>1</v>
@@ -15284,13 +15326,13 @@
     </row>
     <row r="860" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B860">
         <v>2022</v>
       </c>
       <c r="C860" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D860" t="b">
         <v>1</v>
@@ -15299,26 +15341,84 @@
         <v>86</v>
       </c>
     </row>
+    <row r="861" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A861" t="s">
+        <v>61</v>
+      </c>
+      <c r="B861">
+        <v>2022</v>
+      </c>
+      <c r="C861" t="s">
+        <v>27</v>
+      </c>
+      <c r="D861" t="b">
+        <v>1</v>
+      </c>
+      <c r="E861" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="862" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A862" t="s">
+        <v>66</v>
+      </c>
+      <c r="B862">
+        <v>2022</v>
+      </c>
+      <c r="C862" t="s">
+        <v>26</v>
+      </c>
+      <c r="D862" t="b">
+        <v>1</v>
+      </c>
+      <c r="E862" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="4" priority="17" operator="containsText" text="CANDIDATE">
+    <cfRule type="containsText" dxfId="10" priority="23" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:E1048576">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="CANDIDATE">
+  <conditionalFormatting sqref="A1:E235 A238:E1048576">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="PARTY">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="PARTY">
       <formula>NOT(ISERROR(SEARCH("PARTY",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K62:K70">
-    <cfRule type="containsText" dxfId="1" priority="13" operator="containsText" text="CANDIDATE">
+    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="CANDIDATE">
       <formula>NOT(ISERROR(SEARCH("CANDIDATE",K62)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="PARTY">
+    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="PARTY">
       <formula>NOT(ISERROR(SEARCH("PARTY",K62)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A236:D237">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="CANDIDATE">
+      <formula>NOT(ISERROR(SEARCH("CANDIDATE",A236)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="PARTY">
+      <formula>NOT(ISERROR(SEARCH("PARTY",A236)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E236">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="CANDIDATE">
+      <formula>NOT(ISERROR(SEARCH("CANDIDATE",E236)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="PARTY">
+      <formula>NOT(ISERROR(SEARCH("PARTY",E236)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E237">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="CANDIDATE">
+      <formula>NOT(ISERROR(SEARCH("CANDIDATE",E237)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="PARTY">
+      <formula>NOT(ISERROR(SEARCH("PARTY",E237)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/misc./skip_conditions_final.xlsx
+++ b/data/misc./skip_conditions_final.xlsx
@@ -266,7 +266,7 @@
     <t>HOUSE_PARTY_rc</t>
   </si>
   <si>
-    <t>Not elected position, also only 1 respondent</t>
+    <t>Only 1 of 18 DC respondents answered the House vote question.</t>
   </si>
   <si>
     <t>Data is not available (contacted SecState office, the only have physical ballots bound on site)</t>
